--- a/out/Attention_Base_repeat_3_000007.xlsx
+++ b/out/Attention_Base_repeat_3_000007.xlsx
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC39" t="n">
-        <v>-7.712256331345998e-05</v>
+        <v>-1.449758247786667e-05</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>0.889109252280405</v>
+        <v>0.1671357144137942</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC40" t="n">
-        <v>1.779592907008404</v>
+        <v>0.3345297904792994</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.1333258984963202</v>
+        <v>0.02506272324091226</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33536,13 +33536,13 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC41" t="n">
-        <v>1.155942144807108</v>
+        <v>0.217295248853727</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.1667007545622656</v>
+        <v>0.03133661567455685</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34331,13 +34331,13 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC42" t="n">
-        <v>1.356038928517799</v>
+        <v>0.2549096917236587</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.2389645784281521</v>
+        <v>0.04492072728373831</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC43" t="n">
-        <v>1.667361733030028</v>
+        <v>0.3134325408598673</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.2556451129256772</v>
+        <v>0.04805662836548041</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC44" t="n">
-        <v>1.939704871897068</v>
+        <v>0.3646280941901857</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.2709315542955592</v>
+        <v>0.05092960205869598</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC45" t="n">
-        <v>2.225943688836998</v>
+        <v>0.418435782998105</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1222670373213373</v>
+        <v>0.02298424804357823</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC46" t="n">
-        <v>2.19931958941948</v>
+        <v>0.413430878010174</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.05904874746033055</v>
+        <v>0.01109806705231361</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC47" t="n">
-        <v>2.19505546025556</v>
+        <v>0.4126276596408936</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.02813558306727647</v>
+        <v>0.005285894773425655</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC48" t="n">
-        <v>2.192229698691393</v>
+        <v>0.4120930428435143</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.008333563627179606</v>
+        <v>0.00156229537677121</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC49" t="n">
-        <v>2.180734450292196</v>
+        <v>0.409927958603533</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.005510641582937633</v>
+        <v>0.001032186697105211</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC50" t="n">
-        <v>2.18341892269172</v>
+        <v>0.4104286552293966</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.002817967231921131</v>
+        <v>0.0005253518082974867</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC51" t="n">
-        <v>2.183540957973626</v>
+        <v>0.4104475398539587</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001439560167255453</v>
+        <v>0.0002667987771142664</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC52" t="n">
-        <v>2.183599447234295</v>
+        <v>0.4104544855685099</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0005376864856202011</v>
+        <v>9.717946381970313e-05</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC53" t="n">
-        <v>2.183234922977324</v>
+        <v>0.4103818398024654</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0002911771458358382</v>
+        <v>5.027540047632636e-05</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC54" t="n">
-        <v>2.183278531161338</v>
+        <v>0.4103859797277339</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001372566611499408</v>
+        <v>2.202081831898316e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC55" t="n">
-        <v>2.183262475273386</v>
+        <v>0.4103788854843332</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>8.355596056915365e-05</v>
+        <v>1.172723699639569e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC56" t="n">
-        <v>2.183291468911106</v>
+        <v>0.4103803065047913</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>4.132161208684532e-05</v>
+        <v>3.234953259883613e-06</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC57" t="n">
-        <v>2.183290504722986</v>
+        <v>0.4103760694510615</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.698004887727391e-05</v>
+        <v>-1.003627476859289e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC58" t="n">
-        <v>2.183284113910244</v>
+        <v>0.4103707917749614</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>9.070610155389825e-06</v>
+        <v>-2.441707244474577e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC59" t="n">
-        <v>2.1832855457952</v>
+        <v>0.4103671906183565</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.993667665820105e-06</v>
+        <v>-3.834388722363316e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC60" t="n">
-        <v>2.18327917324003</v>
+        <v>0.4103618481876552</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-1.911892527543644e-06</v>
+        <v>-3.970630842514548e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC61" t="n">
-        <v>2.183273351047698</v>
+        <v>0.4103565741235449</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-3.887371769088796e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC62" t="n">
-        <v>2.183268599772485</v>
+        <v>0.4103566574826492</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-4.031182895915095e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC63" t="n">
-        <v>2.183263310624922</v>
+        <v>0.4103565134987417</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC64" t="n">
-        <v>2.183263287890621</v>
+        <v>0.4103564907644403</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC65" t="n">
-        <v>2.183263606170838</v>
+        <v>0.410356809044657</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC66" t="n">
-        <v>2.183264697417295</v>
+        <v>0.4103579002911139</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC67" t="n">
-        <v>2.183264007810159</v>
+        <v>0.4103572106839779</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3</v>
+        <v>2.686681742285026</v>
       </c>
       <c r="JC68" t="n">
-        <v>2.183264038122561</v>
+        <v>0.4103572409963797</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3</v>
+        <v>2.686681742285026</v>
       </c>
       <c r="JC69" t="n">
-        <v>2.18326384867005</v>
+        <v>0.4103570515438695</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.3</v>
+        <v>2.686681742285026</v>
       </c>
       <c r="JC70" t="n">
-        <v>2.183263901716753</v>
+        <v>0.4103571045905724</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.3</v>
+        <v>2.686681742285026</v>
       </c>
       <c r="JC71" t="n">
-        <v>2.183263954763456</v>
+        <v>0.4103571576372753</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.3</v>
+        <v>2.686681742285026</v>
       </c>
       <c r="JC72" t="n">
-        <v>2.183263916872954</v>
+        <v>0.4103571197467732</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.3</v>
+        <v>2.686681742285026</v>
       </c>
       <c r="JC73" t="n">
-        <v>2.183263788045247</v>
+        <v>0.4103569909190666</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.3</v>
+        <v>2.686681742285026</v>
       </c>
       <c r="JC74" t="n">
-        <v>2.18326364406134</v>
+        <v>0.4103568469351591</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3</v>
+        <v>2.686681742285026</v>
       </c>
       <c r="JC75" t="n">
-        <v>2.183263484921231</v>
+        <v>0.4103566877950507</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3</v>
+        <v>2.686681742285026</v>
       </c>
       <c r="JC76" t="n">
-        <v>2.183263537967934</v>
+        <v>0.4103567408417536</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3</v>
+        <v>2.086681742285026</v>
       </c>
       <c r="JC77" t="n">
-        <v>2.183263484921231</v>
+        <v>0.4103566877950507</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.3</v>
+        <v>2.086681742285026</v>
       </c>
       <c r="JC78" t="n">
-        <v>2.183263484921231</v>
+        <v>0.4103566877950507</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.3</v>
+        <v>2.086681742285026</v>
       </c>
       <c r="JC79" t="n">
-        <v>2.183263303046822</v>
+        <v>0.4103565059206411</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.3</v>
+        <v>2.086681742285026</v>
       </c>
       <c r="JC80" t="n">
-        <v>2.183263469765031</v>
+        <v>0.4103566726388498</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.3</v>
+        <v>2.086681742285026</v>
       </c>
       <c r="JC81" t="n">
-        <v>2.183263666795641</v>
+        <v>0.4103568696694602</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.3</v>
+        <v>2.086681742285026</v>
       </c>
       <c r="JC82" t="n">
-        <v>2.183263507655533</v>
+        <v>0.4103567105293519</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.3</v>
+        <v>2.086681742285026</v>
       </c>
       <c r="JC83" t="n">
-        <v>2.183263545546035</v>
+        <v>0.4103567484198539</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.3</v>
+        <v>2.086681742285026</v>
       </c>
       <c r="JC84" t="n">
-        <v>2.183263742576645</v>
+        <v>0.410356945450464</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.3</v>
+        <v>2.086681742285026</v>
       </c>
       <c r="JC85" t="n">
-        <v>2.183263719842344</v>
+        <v>0.4103569227161629</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.3</v>
+        <v>2.086681742285026</v>
       </c>
       <c r="JC86" t="n">
-        <v>2.183263568280336</v>
+        <v>0.410356771154155</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.3</v>
+        <v>2.086681742285026</v>
       </c>
       <c r="JC87" t="n">
-        <v>2.183263492499332</v>
+        <v>0.410356695373151</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.3</v>
+        <v>2.086681742285026</v>
       </c>
       <c r="JC88" t="n">
-        <v>2.183263591014637</v>
+        <v>0.4103567938884562</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3</v>
+        <v>2.086681742285026</v>
       </c>
       <c r="JC89" t="n">
-        <v>2.183263598592738</v>
+        <v>0.4103568014665565</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.3</v>
+        <v>2.086681742285026</v>
       </c>
       <c r="JC90" t="n">
-        <v>2.183263863826252</v>
+        <v>0.4103570667000704</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3</v>
+        <v>2.086681742285026</v>
       </c>
       <c r="JC91" t="n">
-        <v>2.183263568280336</v>
+        <v>0.410356771154155</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3</v>
+        <v>2.086681742285026</v>
       </c>
       <c r="JC92" t="n">
-        <v>2.183263810779549</v>
+        <v>0.4103570136533677</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.3</v>
+        <v>2.086681742285026</v>
       </c>
       <c r="JC93" t="n">
-        <v>2.183263894138653</v>
+        <v>0.4103570970124721</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC94" t="n">
-        <v>2.183263727420444</v>
+        <v>0.4103569302942634</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3</v>
+        <v>2.086681742285026</v>
       </c>
       <c r="JC95" t="n">
-        <v>2.183263916872954</v>
+        <v>0.4103571197467732</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC96" t="n">
-        <v>2.183263568280336</v>
+        <v>0.410356771154155</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.3</v>
+        <v>2.086681742285026</v>
       </c>
       <c r="JC97" t="n">
-        <v>2.183263363671625</v>
+        <v>0.4103565665454443</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.3</v>
+        <v>2.086681742285026</v>
       </c>
       <c r="JC98" t="n">
-        <v>2.183263477343131</v>
+        <v>0.4103566802169504</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC99" t="n">
-        <v>2.183263492499332</v>
+        <v>0.410356695373151</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC100" t="n">
-        <v>2.18326325757822</v>
+        <v>0.4103564604520388</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC101" t="n">
-        <v>2.183263318203023</v>
+        <v>0.410356521076842</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC102" t="n">
-        <v>2.183263189375316</v>
+        <v>0.4103563922491353</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC103" t="n">
-        <v>2.183263325781123</v>
+        <v>0.4103565286549423</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.3</v>
+        <v>2.086681742285026</v>
       </c>
       <c r="JC104" t="n">
-        <v>2.183263500077433</v>
+        <v>0.4103567029512515</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3</v>
+        <v>2.686681742285026</v>
       </c>
       <c r="JC105" t="n">
-        <v>2.18326364406134</v>
+        <v>0.4103568469351591</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.3</v>
+        <v>-0.5212238253023744</v>
       </c>
       <c r="JC106" t="n">
-        <v>2.183263477343131</v>
+        <v>0.4103566802169504</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.3</v>
+        <v>-0.5212238253023744</v>
       </c>
       <c r="JC107" t="n">
-        <v>2.183263469765031</v>
+        <v>0.4103566726388498</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC108" t="n">
-        <v>2.183263181797216</v>
+        <v>0.4103563846710347</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC109" t="n">
-        <v>2.183263196953417</v>
+        <v>0.4103563998272356</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC110" t="n">
-        <v>2.183263424296428</v>
+        <v>0.4103566271702475</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC111" t="n">
-        <v>2.183263409140228</v>
+        <v>0.4103566120140467</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC112" t="n">
-        <v>2.183263515233633</v>
+        <v>0.4103567181074522</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC113" t="n">
-        <v>2.183263242422019</v>
+        <v>0.4103564452958379</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC114" t="n">
-        <v>2.183263340937324</v>
+        <v>0.4103565438111432</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC115" t="n">
-        <v>2.183263492499332</v>
+        <v>0.410356695373151</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC116" t="n">
-        <v>2.183263507655533</v>
+        <v>0.4103567105293519</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC117" t="n">
-        <v>2.183263484921231</v>
+        <v>0.4103566877950507</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC118" t="n">
-        <v>2.183263568280336</v>
+        <v>0.410356771154155</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.3</v>
+        <v>2.686681742285026</v>
       </c>
       <c r="JC119" t="n">
-        <v>2.183263666795641</v>
+        <v>0.4103568696694602</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3</v>
+        <v>-0.5212238253023744</v>
       </c>
       <c r="JC120" t="n">
-        <v>2.183263500077433</v>
+        <v>0.4103567029512515</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3</v>
+        <v>-0.5212238253023744</v>
       </c>
       <c r="JC121" t="n">
-        <v>2.183263484921231</v>
+        <v>0.4103566877950507</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC122" t="n">
-        <v>2.18326345460883</v>
+        <v>0.4103566574826492</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC123" t="n">
-        <v>2.183263439452629</v>
+        <v>0.4103566423264484</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC124" t="n">
-        <v>2.183263477343131</v>
+        <v>0.4103566802169504</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC125" t="n">
-        <v>2.183263492499332</v>
+        <v>0.410356695373151</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.3</v>
+        <v>-1.121223825302375</v>
       </c>
       <c r="JC126" t="n">
-        <v>2.183263484921231</v>
+        <v>0.4103566877950507</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention_Base_repeat_3_000007.xlsx
+++ b/out/Attention_Base_repeat_3_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA8" t="n">
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,17 +31942,17 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC39" t="n">
-        <v>-7.712256331345998e-05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -32733,21 +32733,21 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>0.889109252280405</v>
+        <v>0</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC40" t="n">
-        <v>1.779592907008404</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -33528,21 +33528,21 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.1333258984963202</v>
+        <v>0</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC41" t="n">
-        <v>1.155942144807108</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -34323,21 +34323,21 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.1667007545622656</v>
+        <v>0</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC42" t="n">
-        <v>1.356038928517799</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -35118,21 +35118,21 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.2389645784281521</v>
+        <v>0</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA43" t="n">
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC43" t="n">
-        <v>1.667361733030028</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -35913,21 +35913,21 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.2556451129256772</v>
+        <v>0</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA44" t="n">
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC44" t="n">
-        <v>1.939704871897068</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -36708,21 +36708,21 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.2709315542955592</v>
+        <v>0</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA45" t="n">
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC45" t="n">
-        <v>2.225943688836998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1222670373213373</v>
+        <v>0</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA46" t="n">
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC46" t="n">
-        <v>2.19931958941948</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -38298,21 +38298,21 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.05904874746033055</v>
+        <v>0</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC47" t="n">
-        <v>2.19505546025556</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -39093,21 +39093,21 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.02813558306727647</v>
+        <v>0</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC48" t="n">
-        <v>2.192229698691393</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -39888,21 +39888,21 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.008333563627179606</v>
+        <v>0</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA49" t="n">
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC49" t="n">
-        <v>2.180734450292196</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -40683,21 +40683,21 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.005510641582937633</v>
+        <v>0</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC50" t="n">
-        <v>2.18341892269172</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -41478,21 +41478,21 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.002817967231921131</v>
+        <v>0</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC51" t="n">
-        <v>2.183540957973626</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -42273,21 +42273,21 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001439560167255453</v>
+        <v>0</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA52" t="n">
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC52" t="n">
-        <v>2.183599447234295</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -43068,21 +43068,21 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0005376864856202011</v>
+        <v>0</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC53" t="n">
-        <v>2.183234922977324</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -43863,21 +43863,21 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0002911771458358382</v>
+        <v>0</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA54" t="n">
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC54" t="n">
-        <v>2.183278531161338</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -44658,21 +44658,21 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001372566611499408</v>
+        <v>0</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA55" t="n">
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC55" t="n">
-        <v>2.183262475273386</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -45453,21 +45453,21 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>8.355596056915365e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA56" t="n">
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC56" t="n">
-        <v>2.183291468911106</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -46248,21 +46248,21 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>4.132161208684532e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA57" t="n">
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC57" t="n">
-        <v>2.183290504722986</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -47043,21 +47043,21 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.698004887727391e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA58" t="n">
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC58" t="n">
-        <v>2.183284113910244</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -47838,21 +47838,21 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>9.070610155389825e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA59" t="n">
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC59" t="n">
-        <v>2.1832855457952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -48633,21 +48633,21 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.993667665820105e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA60" t="n">
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC60" t="n">
-        <v>2.18327917324003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -49428,21 +49428,21 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-1.911892527543644e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA61" t="n">
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC61" t="n">
-        <v>2.183273351047698</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -50223,21 +50223,21 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-3.887371769088796e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA62" t="n">
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC62" t="n">
-        <v>2.183268599772485</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -51018,21 +51018,21 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-4.031182895915095e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA63" t="n">
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC63" t="n">
-        <v>2.183263310624922</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -51817,17 +51817,17 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA64" t="n">
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC64" t="n">
-        <v>2.183263287890621</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -52612,17 +52612,17 @@
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA65" t="n">
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC65" t="n">
-        <v>2.183263606170838</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -53407,17 +53407,17 @@
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA66" t="n">
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC66" t="n">
-        <v>2.183264697417295</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -54202,17 +54202,17 @@
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA67" t="n">
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC67" t="n">
-        <v>2.183264007810159</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -54997,17 +54997,17 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA68" t="n">
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC68" t="n">
-        <v>2.183264038122561</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -55792,17 +55792,17 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA69" t="n">
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC69" t="n">
-        <v>2.18326384867005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -56587,17 +56587,17 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA70" t="n">
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC70" t="n">
-        <v>2.183263901716753</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -57382,17 +57382,17 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA71" t="n">
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC71" t="n">
-        <v>2.183263954763456</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -58177,17 +58177,17 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA72" t="n">
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC72" t="n">
-        <v>2.183263916872954</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -58972,17 +58972,17 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA73" t="n">
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC73" t="n">
-        <v>2.183263788045247</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -59767,17 +59767,17 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA74" t="n">
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC74" t="n">
-        <v>2.18326364406134</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -60562,17 +60562,17 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA75" t="n">
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC75" t="n">
-        <v>2.183263484921231</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -61357,17 +61357,17 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA76" t="n">
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC76" t="n">
-        <v>2.183263537967934</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -62152,17 +62152,17 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA77" t="n">
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC77" t="n">
-        <v>2.183263484921231</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -62947,17 +62947,17 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA78" t="n">
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC78" t="n">
-        <v>2.183263484921231</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -63742,17 +63742,17 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA79" t="n">
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC79" t="n">
-        <v>2.183263303046822</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -64537,17 +64537,17 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA80" t="n">
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC80" t="n">
-        <v>2.183263469765031</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -65332,17 +65332,17 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA81" t="n">
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC81" t="n">
-        <v>2.183263666795641</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -66127,17 +66127,17 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA82" t="n">
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC82" t="n">
-        <v>2.183263507655533</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -66922,17 +66922,17 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA83" t="n">
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC83" t="n">
-        <v>2.183263545546035</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -67717,17 +67717,17 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA84" t="n">
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC84" t="n">
-        <v>2.183263742576645</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -68512,17 +68512,17 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA85" t="n">
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC85" t="n">
-        <v>2.183263719842344</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -69307,17 +69307,17 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA86" t="n">
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC86" t="n">
-        <v>2.183263568280336</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -70102,17 +70102,17 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA87" t="n">
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC87" t="n">
-        <v>2.183263492499332</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -70897,17 +70897,17 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA88" t="n">
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC88" t="n">
-        <v>2.183263591014637</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -71692,17 +71692,17 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA89" t="n">
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC89" t="n">
-        <v>2.183263598592738</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -72487,17 +72487,17 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA90" t="n">
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC90" t="n">
-        <v>2.183263863826252</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -73282,17 +73282,17 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA91" t="n">
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC91" t="n">
-        <v>2.183263568280336</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -74077,17 +74077,17 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA92" t="n">
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC92" t="n">
-        <v>2.183263810779549</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -74872,17 +74872,17 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA93" t="n">
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC93" t="n">
-        <v>2.183263894138653</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -75667,17 +75667,17 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA94" t="n">
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC94" t="n">
-        <v>2.183263727420444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -76462,17 +76462,17 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA95" t="n">
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC95" t="n">
-        <v>2.183263916872954</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -77257,17 +77257,17 @@
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA96" t="n">
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC96" t="n">
-        <v>2.183263568280336</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -78052,17 +78052,17 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA97" t="n">
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC97" t="n">
-        <v>2.183263363671625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -78847,17 +78847,17 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA98" t="n">
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC98" t="n">
-        <v>2.183263477343131</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -79642,17 +79642,17 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA99" t="n">
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC99" t="n">
-        <v>2.183263492499332</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -80437,17 +80437,17 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA100" t="n">
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC100" t="n">
-        <v>2.18326325757822</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -81232,17 +81232,17 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA101" t="n">
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC101" t="n">
-        <v>2.183263318203023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -82027,17 +82027,17 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA102" t="n">
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC102" t="n">
-        <v>2.183263189375316</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -82822,17 +82822,17 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA103" t="n">
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC103" t="n">
-        <v>2.183263325781123</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -83617,17 +83617,17 @@
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA104" t="n">
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC104" t="n">
-        <v>2.183263500077433</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -84412,17 +84412,17 @@
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA105" t="n">
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC105" t="n">
-        <v>2.18326364406134</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -85207,17 +85207,17 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA106" t="n">
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC106" t="n">
-        <v>2.183263477343131</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -86002,17 +86002,17 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA107" t="n">
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC107" t="n">
-        <v>2.183263469765031</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -86797,17 +86797,17 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA108" t="n">
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC108" t="n">
-        <v>2.183263181797216</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -87592,17 +87592,17 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA109" t="n">
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC109" t="n">
-        <v>2.183263196953417</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -88387,17 +88387,17 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA110" t="n">
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC110" t="n">
-        <v>2.183263424296428</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -89182,17 +89182,17 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA111" t="n">
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC111" t="n">
-        <v>2.183263409140228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -89977,17 +89977,17 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA112" t="n">
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC112" t="n">
-        <v>2.183263515233633</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -90772,17 +90772,17 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA113" t="n">
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC113" t="n">
-        <v>2.183263242422019</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -91567,17 +91567,17 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA114" t="n">
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC114" t="n">
-        <v>2.183263340937324</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -92362,17 +92362,17 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA115" t="n">
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC115" t="n">
-        <v>2.183263492499332</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -93157,17 +93157,17 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA116" t="n">
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC116" t="n">
-        <v>2.183263507655533</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -93952,17 +93952,17 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA117" t="n">
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC117" t="n">
-        <v>2.183263484921231</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -94747,17 +94747,17 @@
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA118" t="n">
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC118" t="n">
-        <v>2.183263568280336</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -95542,17 +95542,17 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA119" t="n">
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC119" t="n">
-        <v>2.183263666795641</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -96337,17 +96337,17 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA120" t="n">
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC120" t="n">
-        <v>2.183263500077433</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -97132,17 +97132,17 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA121" t="n">
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC121" t="n">
-        <v>2.183263484921231</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -97927,17 +97927,17 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA122" t="n">
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC122" t="n">
-        <v>2.18326345460883</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -98722,17 +98722,17 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA123" t="n">
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC123" t="n">
-        <v>2.183263439452629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -99517,17 +99517,17 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA124" t="n">
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC124" t="n">
-        <v>2.183263477343131</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -100312,17 +100312,17 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA125" t="n">
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC125" t="n">
-        <v>2.183263492499332</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -101103,21 +101103,21 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>-3.857095742388521e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Sell (Force)</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA126" t="n">
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC126" t="n">
-        <v>2.183263484921231</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention_Base_repeat_3_000007.xlsx
+++ b/out/Attention_Base_repeat_3_000007.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.004696219228208065</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.005443836562335491</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.004027030430734158</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.01415034011006355</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.01560217421501875</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.01506191492080688</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.01332693919539452</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.01265742629766464</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.01186651829630136</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.01138549670577049</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.01071186363697052</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.009936561807990074</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.009801621548831463</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.009579496458172798</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.009778613224625587</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.009614352136850357</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.009518799372017384</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.009223191067576408</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.009361999109387398</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.009401231072843075</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.009769927710294724</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.01078097149729729</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.01109042577445507</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.01106384210288525</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.01093714311718941</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.01072639971971512</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.01040953490883112</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.01046436931937933</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.01040671020746231</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.01028658263385296</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.01001180149614811</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.009836664423346519</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.009711474180221558</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.009637642651796341</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.01017231494188309</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.01355281099677086</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.01494872197508812</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,17 +31942,17 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.01611394062638283</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC39" t="n">
-        <v>0</v>
+        <v>-0.0001762581139509566</v>
       </c>
     </row>
     <row r="40">
@@ -32733,21 +32733,21 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>0</v>
+        <v>2.031995661651695</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.01729941368103027</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
-        <v>0</v>
+        <v>4.067132573440041</v>
       </c>
     </row>
     <row r="41">
@@ -33528,21 +33528,21 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0</v>
+        <v>0.304706836431729</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.01802016049623489</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
-        <v>0</v>
+        <v>2.641823215454815</v>
       </c>
     </row>
     <row r="42">
@@ -34323,21 +34323,21 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0</v>
+        <v>0.3809826339917982</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.01833935268223286</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
-        <v>0</v>
+        <v>3.099130150153705</v>
       </c>
     </row>
     <row r="43">
@@ -35118,21 +35118,21 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0</v>
+        <v>0.5461367990545677</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.02088913507759571</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
-        <v>0</v>
+        <v>3.810636331820818</v>
       </c>
     </row>
     <row r="44">
@@ -35913,21 +35913,21 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0</v>
+        <v>0.5842581963286199</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.02514833770692348</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
-        <v>0</v>
+        <v>4.43305701572845</v>
       </c>
     </row>
     <row r="45">
@@ -36708,21 +36708,21 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0</v>
+        <v>0.619196663161341</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.034867312759161</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>0</v>
+        <v>5.087235660467096</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0</v>
+        <v>0.2794319377854967</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.05401160567998886</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>0</v>
+        <v>5.026388322909726</v>
       </c>
     </row>
     <row r="47">
@@ -38298,21 +38298,21 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0</v>
+        <v>0.1349522109205024</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.04296502843499184</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC47" t="n">
-        <v>0</v>
+        <v>5.016642981444461</v>
       </c>
     </row>
     <row r="48">
@@ -39093,21 +39093,21 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0</v>
+        <v>0.06430132361609035</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.04894167184829712</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>0</v>
+        <v>5.010184959644628</v>
       </c>
     </row>
     <row r="49">
@@ -39888,21 +39888,21 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0</v>
+        <v>0.01905167046229239</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.04166878759860992</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>0</v>
+        <v>4.983919210836554</v>
       </c>
     </row>
     <row r="50">
@@ -40683,21 +40683,21 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0</v>
+        <v>0.01260080754943257</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.04416384175419807</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC50" t="n">
-        <v>0</v>
+        <v>4.990060604748933</v>
       </c>
     </row>
     <row r="51">
@@ -41478,21 +41478,21 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0</v>
+        <v>0.00644679370502156</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.04139304161071777</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC51" t="n">
-        <v>0</v>
+        <v>4.990345910255853</v>
       </c>
     </row>
     <row r="52">
@@ -42273,21 +42273,21 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0</v>
+        <v>0.003295845148732146</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.04272878915071487</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC52" t="n">
-        <v>0</v>
+        <v>4.990485984322567</v>
       </c>
     </row>
     <row r="53">
@@ -43068,21 +43068,21 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0</v>
+        <v>0.001235534379262914</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.04199239611625671</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC53" t="n">
-        <v>0</v>
+        <v>4.9896594645375</v>
       </c>
     </row>
     <row r="54">
@@ -43863,21 +43863,21 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0</v>
+        <v>0.0006715049013520539</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.0414368137717247</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC54" t="n">
-        <v>0</v>
+        <v>4.989765491587336</v>
       </c>
     </row>
     <row r="55">
@@ -44658,21 +44658,21 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0</v>
+        <v>0.0003208392797289147</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.0410120040178299</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC55" t="n">
-        <v>0</v>
+        <v>4.98973523747574</v>
       </c>
     </row>
     <row r="56">
@@ -45453,21 +45453,21 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0</v>
+        <v>0.0001967107990741833</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.04241777956485748</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC56" t="n">
-        <v>0</v>
+        <v>4.989807667428328</v>
       </c>
     </row>
     <row r="57">
@@ -46248,21 +46248,21 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0</v>
+        <v>9.999565406351607e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.03972765058279037</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC57" t="n">
-        <v>0</v>
+        <v>4.98981186073719</v>
       </c>
     </row>
     <row r="58">
@@ -47043,21 +47043,21 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0</v>
+        <v>4.595374967004406e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.059731625020504</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC58" t="n">
-        <v>0</v>
+        <v>4.989803676537635</v>
       </c>
     </row>
     <row r="59">
@@ -47838,21 +47838,21 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0</v>
+        <v>2.82578058218305e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.0572802871465683</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC59" t="n">
-        <v>0</v>
+        <v>4.989813216435479</v>
       </c>
     </row>
     <row r="60">
@@ -48633,21 +48633,21 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0</v>
+        <v>1.015294660927689e-05</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.04993191361427307</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0</v>
+        <v>4.989805242565942</v>
       </c>
     </row>
     <row r="61">
@@ -49428,21 +49428,21 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0</v>
+        <v>1.176214944912711e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.04834128171205521</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>0</v>
+        <v>4.989798461775472</v>
       </c>
     </row>
     <row r="62">
@@ -50223,21 +50223,21 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0</v>
+        <v>-1.662115307266386e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.04882674291729927</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>0</v>
+        <v>4.989794041231621</v>
       </c>
     </row>
     <row r="63">
@@ -51018,21 +51018,21 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0</v>
+        <v>-3.062365791830193e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.04789893329143524</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>0</v>
+        <v>4.989788462936497</v>
       </c>
     </row>
     <row r="64">
@@ -51813,21 +51813,21 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0</v>
+        <v>-4.053889915940302e-06</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.05107709765434265</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>0</v>
+        <v>4.98978341631543</v>
       </c>
     </row>
     <row r="65">
@@ -52612,17 +52612,17 @@
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.06897243857383728</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>0</v>
+        <v>4.989783734595646</v>
       </c>
     </row>
     <row r="66">
@@ -53407,17 +53407,17 @@
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.3078725039958954</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>0</v>
+        <v>4.989784825842103</v>
       </c>
     </row>
     <row r="67">
@@ -54202,17 +54202,17 @@
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.1868009567260742</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>0</v>
+        <v>4.989784136234967</v>
       </c>
     </row>
     <row r="68">
@@ -54997,17 +54997,17 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.1287883967161179</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>0</v>
+        <v>4.989784166547369</v>
       </c>
     </row>
     <row r="69">
@@ -55792,17 +55792,17 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.1099819839000702</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>0</v>
+        <v>4.989783977094859</v>
       </c>
     </row>
     <row r="70">
@@ -56587,17 +56587,17 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.1049025878310204</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC70" t="n">
-        <v>0</v>
+        <v>4.989784030141562</v>
       </c>
     </row>
     <row r="71">
@@ -57382,17 +57382,17 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.09168299287557602</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC71" t="n">
-        <v>0</v>
+        <v>4.989784083188264</v>
       </c>
     </row>
     <row r="72">
@@ -58177,17 +58177,17 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0.08686299622058868</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC72" t="n">
-        <v>0</v>
+        <v>4.989784045297762</v>
       </c>
     </row>
     <row r="73">
@@ -58972,17 +58972,17 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.085626021027565</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC73" t="n">
-        <v>0</v>
+        <v>4.989783916470055</v>
       </c>
     </row>
     <row r="74">
@@ -59767,17 +59767,17 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.08150826394557953</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC74" t="n">
-        <v>0</v>
+        <v>4.989783772486148</v>
       </c>
     </row>
     <row r="75">
@@ -60562,17 +60562,17 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.07757750898599625</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC75" t="n">
-        <v>0</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
     <row r="76">
@@ -61357,17 +61357,17 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.07778400182723999</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC76" t="n">
-        <v>0</v>
+        <v>4.989783666392743</v>
       </c>
     </row>
     <row r="77">
@@ -62152,17 +62152,17 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.07132463157176971</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC77" t="n">
-        <v>0</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
     <row r="78">
@@ -62947,17 +62947,17 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.07309487462043762</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC78" t="n">
-        <v>0</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
     <row r="79">
@@ -63742,17 +63742,17 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.07521594315767288</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC79" t="n">
-        <v>0</v>
+        <v>4.989783431471631</v>
       </c>
     </row>
     <row r="80">
@@ -64537,17 +64537,17 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.0809498056769371</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="JC80" t="n">
-        <v>0</v>
+        <v>4.989783598189839</v>
       </c>
     </row>
     <row r="81">
@@ -65332,17 +65332,17 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.0753575935959816</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="JC81" t="n">
-        <v>0</v>
+        <v>4.98978379522045</v>
       </c>
     </row>
     <row r="82">
@@ -66127,17 +66127,17 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.07009420543909073</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>0</v>
+        <v>4.989783636080341</v>
       </c>
     </row>
     <row r="83">
@@ -66922,17 +66922,17 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.07775266468524933</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="JC83" t="n">
-        <v>0</v>
+        <v>4.989783673970843</v>
       </c>
     </row>
     <row r="84">
@@ -67717,17 +67717,17 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.08516061305999756</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>0</v>
+        <v>4.989783871001453</v>
       </c>
     </row>
     <row r="85">
@@ -68512,17 +68512,17 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.07767033576965332</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>0</v>
+        <v>4.989783848267152</v>
       </c>
     </row>
     <row r="86">
@@ -69307,17 +69307,17 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.0712863951921463</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC86" t="n">
-        <v>0</v>
+        <v>4.989783696705144</v>
       </c>
     </row>
     <row r="87">
@@ -70102,17 +70102,17 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.0705779567360878</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>0</v>
+        <v>4.989783620924141</v>
       </c>
     </row>
     <row r="88">
@@ -70897,17 +70897,17 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.07236145436763763</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>0</v>
+        <v>4.989783719439446</v>
       </c>
     </row>
     <row r="89">
@@ -71692,17 +71692,17 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.08005587756633759</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC89" t="n">
-        <v>0</v>
+        <v>4.989783727017546</v>
       </c>
     </row>
     <row r="90">
@@ -72487,17 +72487,17 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.07933773100376129</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>0</v>
+        <v>4.98978399225106</v>
       </c>
     </row>
     <row r="91">
@@ -73282,17 +73282,17 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.07296140491962433</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC91" t="n">
-        <v>0</v>
+        <v>4.989783696705144</v>
       </c>
     </row>
     <row r="92">
@@ -74077,17 +74077,17 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.08228278905153275</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>0</v>
+        <v>4.989783939204357</v>
       </c>
     </row>
     <row r="93">
@@ -74872,17 +74872,17 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.07621277123689651</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>0</v>
+        <v>4.989784022563462</v>
       </c>
     </row>
     <row r="94">
@@ -75667,17 +75667,17 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.0975448414683342</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>0</v>
+        <v>4.989783855845253</v>
       </c>
     </row>
     <row r="95">
@@ -76462,17 +76462,17 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.08576015383005142</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>0</v>
+        <v>4.989784045297762</v>
       </c>
     </row>
     <row r="96">
@@ -77257,17 +77257,17 @@
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.07435471564531326</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>0</v>
+        <v>4.989783696705144</v>
       </c>
     </row>
     <row r="97">
@@ -78052,17 +78052,17 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.06676319241523743</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>0</v>
+        <v>4.989783492096433</v>
       </c>
     </row>
     <row r="98">
@@ -78847,17 +78847,17 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.06600154936313629</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>0</v>
+        <v>4.989783605767939</v>
       </c>
     </row>
     <row r="99">
@@ -79642,17 +79642,17 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.06760936230421066</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>0</v>
+        <v>4.989783620924141</v>
       </c>
     </row>
     <row r="100">
@@ -80437,17 +80437,17 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.0643220990896225</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>0</v>
+        <v>4.989783386003029</v>
       </c>
     </row>
     <row r="101">
@@ -81232,17 +81232,17 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.06193548440933228</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC101" t="n">
-        <v>0</v>
+        <v>4.989783446627831</v>
       </c>
     </row>
     <row r="102">
@@ -82027,17 +82027,17 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.06004297733306885</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC102" t="n">
-        <v>0</v>
+        <v>4.989783317800124</v>
       </c>
     </row>
     <row r="103">
@@ -82822,17 +82822,17 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.07228811830282211</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC103" t="n">
-        <v>0</v>
+        <v>4.989783454205933</v>
       </c>
     </row>
     <row r="104">
@@ -83617,17 +83617,17 @@
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.06700876355171204</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>0</v>
+        <v>4.989783628502241</v>
       </c>
     </row>
     <row r="105">
@@ -84412,17 +84412,17 @@
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.0656435638666153</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>0</v>
+        <v>4.989783772486148</v>
       </c>
     </row>
     <row r="106">
@@ -85207,17 +85207,17 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.06571034342050552</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0</v>
+        <v>4.989783605767939</v>
       </c>
     </row>
     <row r="107">
@@ -86002,17 +86002,17 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0.06357408314943314</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>0</v>
+        <v>4.989783598189839</v>
       </c>
     </row>
     <row r="108">
@@ -86797,17 +86797,17 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.05764947831630707</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>0</v>
+        <v>4.989783310222024</v>
       </c>
     </row>
     <row r="109">
@@ -87592,17 +87592,17 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.05817872285842896</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>0</v>
+        <v>4.989783325378225</v>
       </c>
     </row>
     <row r="110">
@@ -88387,17 +88387,17 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.05933021008968353</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>0</v>
+        <v>4.989783552721237</v>
       </c>
     </row>
     <row r="111">
@@ -89182,17 +89182,17 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.06219212710857391</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>0</v>
+        <v>4.989783537565036</v>
       </c>
     </row>
     <row r="112">
@@ -89977,17 +89977,17 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.05883263796567917</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>0</v>
+        <v>4.989783643658441</v>
       </c>
     </row>
     <row r="113">
@@ -90772,17 +90772,17 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.05595897138118744</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>0</v>
+        <v>4.989783370846827</v>
       </c>
     </row>
     <row r="114">
@@ -91567,17 +91567,17 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.05780859291553497</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>0</v>
+        <v>4.989783469362132</v>
       </c>
     </row>
     <row r="115">
@@ -92362,17 +92362,17 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.05904868990182877</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>0</v>
+        <v>4.989783620924141</v>
       </c>
     </row>
     <row r="116">
@@ -93157,17 +93157,17 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.05859215557575226</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>0</v>
+        <v>4.989783636080341</v>
       </c>
     </row>
     <row r="117">
@@ -93952,17 +93952,17 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.05916117876768112</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>0</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
     <row r="118">
@@ -94747,17 +94747,17 @@
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.06102246791124344</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>0</v>
+        <v>4.989783696705144</v>
       </c>
     </row>
     <row r="119">
@@ -95542,17 +95542,17 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.05825571715831757</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC119" t="n">
-        <v>0</v>
+        <v>4.98978379522045</v>
       </c>
     </row>
     <row r="120">
@@ -96337,17 +96337,17 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.05601782351732254</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>0</v>
+        <v>4.989783628502241</v>
       </c>
     </row>
     <row r="121">
@@ -97132,17 +97132,17 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.05567136406898499</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC121" t="n">
-        <v>0</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
     <row r="122">
@@ -97927,17 +97927,17 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.05541740357875824</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>0</v>
+        <v>4.989783583033638</v>
       </c>
     </row>
     <row r="123">
@@ -98722,17 +98722,17 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.05524221062660217</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC123" t="n">
-        <v>0</v>
+        <v>4.989783567877438</v>
       </c>
     </row>
     <row r="124">
@@ -99517,17 +99517,17 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.05414044111967087</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC124" t="n">
-        <v>0</v>
+        <v>4.989783605767939</v>
       </c>
     </row>
     <row r="125">
@@ -100312,17 +100312,17 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.05559861660003662</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3999999999999996</v>
       </c>
       <c r="JC125" t="n">
-        <v>0</v>
+        <v>4.989783620924141</v>
       </c>
     </row>
     <row r="126">
@@ -101103,21 +101103,21 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>0</v>
+        <v>-3.857095742388521e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell (Force)</t>
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.05754970014095306</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3999999999999995</v>
       </c>
       <c r="JC126" t="n">
-        <v>0</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention_Base_repeat_3_000007.xlsx
+++ b/out/Attention_Base_repeat_3_000007.xlsx
@@ -60569,7 +60569,7 @@
         <v>0.07757750898599625</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC75" t="n">
         <v>4.98978361334604</v>
@@ -61364,7 +61364,7 @@
         <v>0.07778400182723999</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC76" t="n">
         <v>4.989783666392743</v>
@@ -62159,7 +62159,7 @@
         <v>0.07132463157176971</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC77" t="n">
         <v>4.98978361334604</v>
@@ -62954,7 +62954,7 @@
         <v>0.07309487462043762</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.16</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC78" t="n">
         <v>4.98978361334604</v>
@@ -63749,7 +63749,7 @@
         <v>0.07521594315767288</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.16</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC79" t="n">
         <v>4.989783431471631</v>
@@ -64544,7 +64544,7 @@
         <v>0.0809498056769371</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.3</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC80" t="n">
         <v>4.989783598189839</v>
@@ -65339,7 +65339,7 @@
         <v>0.0753575935959816</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.3</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC81" t="n">
         <v>4.98978379522045</v>
@@ -66134,7 +66134,7 @@
         <v>0.07009420543909073</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.4399999999999999</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC82" t="n">
         <v>4.989783636080341</v>
@@ -66929,7 +66929,7 @@
         <v>0.07775266468524933</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.3</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC83" t="n">
         <v>4.989783673970843</v>
@@ -67724,7 +67724,7 @@
         <v>0.08516061305999756</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.4399999999999999</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC84" t="n">
         <v>4.989783871001453</v>
@@ -68519,7 +68519,7 @@
         <v>0.07767033576965332</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.4399999999999999</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC85" t="n">
         <v>4.989783848267152</v>
@@ -69314,7 +69314,7 @@
         <v>0.0712863951921463</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.5799999999999998</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC86" t="n">
         <v>4.989783696705144</v>
@@ -70109,7 +70109,7 @@
         <v>0.0705779567360878</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC87" t="n">
         <v>4.989783620924141</v>
@@ -74084,7 +74084,7 @@
         <v>0.08228278905153275</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC92" t="n">
         <v>4.989783939204357</v>
@@ -74879,7 +74879,7 @@
         <v>0.07621277123689651</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC93" t="n">
         <v>4.989784022563462</v>
